--- a/Result/profitability/4908.xlsx
+++ b/Result/profitability/4908.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6062500000000001</v>
+        <v>0.64625</v>
       </c>
       <c r="N2" t="n">
-        <v>44.47125</v>
+        <v>44.4675</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.66125</v>
+        <v>0.615</v>
       </c>
       <c r="N3" t="n">
-        <v>42.39125000000001</v>
+        <v>42.4225</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.66625</v>
+        <v>0.65625</v>
       </c>
       <c r="N4" t="n">
-        <v>39.8825</v>
+        <v>38.77</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64625</v>
+        <v>0.7125</v>
       </c>
       <c r="N5" t="n">
-        <v>37.74125</v>
+        <v>37.70874999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6825</v>
+        <v>0.705</v>
       </c>
       <c r="N6" t="n">
-        <v>35.1375</v>
+        <v>35.55875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6725</v>
+        <v>0.6825</v>
       </c>
       <c r="N7" t="n">
-        <v>32.5525</v>
+        <v>32.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.675</v>
+        <v>0.6637500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>29.68875</v>
+        <v>29.53875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6437499999999999</v>
+        <v>0.64375</v>
       </c>
       <c r="N11" t="n">
         <v>25.6375</v>
@@ -1899,7 +1899,7 @@
         <v>0.96</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6287499999999999</v>
+        <v>0.62875</v>
       </c>
       <c r="N12" t="n">
         <v>25.71625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>255</v>
+      </c>
+      <c r="D75" t="n">
+        <v>139</v>
+      </c>
+      <c r="E75" t="n">
+        <v>117</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>60</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.52%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>65</v>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.59875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.59875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1184210526315789</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02560819462227915</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.785714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.2600000000000051</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.005662020905923493</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
